--- a/Declaração de Imposto de Renda.xlsx
+++ b/Declaração de Imposto de Renda.xlsx
@@ -1,22 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr codeName="EstaPastaDeTrabalho" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danie\Downloads\estudo FN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E25A94FA-D03B-4D17-BC7B-5CF61E130580}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{33DED770-8B7B-4719-AF21-BEA3AC23432E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{21595B40-B017-4BAA-9E40-1B14F133D7F8}"/>
   </bookViews>
   <sheets>
-    <sheet name="TITULAR" sheetId="3" r:id="rId1"/>
-    <sheet name="INFORMES" sheetId="4" r:id="rId2"/>
-    <sheet name="NOTAS" sheetId="5" r:id="rId3"/>
-    <sheet name="BASE_BANCO" sheetId="6" state="hidden" r:id="rId4"/>
+    <sheet name="LEIA-ME" sheetId="7" r:id="rId1"/>
+    <sheet name="TITULAR" sheetId="3" r:id="rId2"/>
+    <sheet name="INFORMES" sheetId="4" r:id="rId3"/>
+    <sheet name="NOTAS" sheetId="5" r:id="rId4"/>
+    <sheet name="BASE_BANCO" sheetId="6" state="hidden" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="aporte">#REF!</definedName>
@@ -50,7 +51,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="112">
   <si>
     <t>NOME</t>
   </si>
@@ -320,6 +321,72 @@
   </si>
   <si>
     <t>FREELANCE</t>
+  </si>
+  <si>
+    <t>🦁 LIONE IR</t>
+  </si>
+  <si>
+    <t>ORGANIZADOR DE INFORMAÇÕES PARA O IMPOSTO DE RENDA</t>
+  </si>
+  <si>
+    <t>Bem-vindo ao LIONE IR!</t>
+  </si>
+  <si>
+    <t>Esta ferramenta foi desenvolvida no Microsoft Excel para ajudar a organizar informações e documentos necessários à preparação da declaração do Imposto de Renda.</t>
+  </si>
+  <si>
+    <t>📌 COMO UTILIZAR</t>
+  </si>
+  <si>
+    <t>1. TITULAR</t>
+  </si>
+  <si>
+    <t>Preencha os dados cadastrais do contribuinte.</t>
+  </si>
+  <si>
+    <t>2. INFORMES</t>
+  </si>
+  <si>
+    <t>Organize os informes de rendimentos bancários e as informações solicitadas pela planilha.</t>
+  </si>
+  <si>
+    <t>3. NOTAS</t>
+  </si>
+  <si>
+    <t>Registre as entradas financeiras e os documentos previstos na estrutura da ferramenta.</t>
+  </si>
+  <si>
+    <t>⚠️ ORIENTAÇÕES IMPORTANTES</t>
+  </si>
+  <si>
+    <t>Preencha os campos conforme as informações dos seus documentos.</t>
+  </si>
+  <si>
+    <t>Confira os dados antes de utilizá-los na preparação da declaração.</t>
+  </si>
+  <si>
+    <t>Utilize documentos oficiais para conferir rendimentos e informações financeiras.</t>
+  </si>
+  <si>
+    <t>Mantenha uma cópia de segurança do arquivo.</t>
+  </si>
+  <si>
+    <t>Não compartilhe a planilha preenchida com dados pessoais ou financeiros em repositórios públicos.</t>
+  </si>
+  <si>
+    <t>🔒 PRIVACIDADE</t>
+  </si>
+  <si>
+    <t>Os dados inseridos são de responsabilidade do usuário. Utilize uma cópia privada para preencher informações pessoais e financeiras.</t>
+  </si>
+  <si>
+    <t>⚖️ AVISO</t>
+  </si>
+  <si>
+    <t>O LIONE IR é um projeto educacional de organização de informações. Não substitui o programa oficial da Receita Federal nem garante a correção ou a completude de uma declaração.</t>
+  </si>
+  <si>
+    <t>LIONE IR — Organização, clareza e planejamento.</t>
   </si>
 </sst>
 </file>
@@ -336,7 +403,7 @@
     <numFmt numFmtId="168" formatCode="&quot;R$&quot;\ #,##0.00"/>
     <numFmt numFmtId="169" formatCode="mmmm\-yyyy"/>
   </numFmts>
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -465,6 +532,38 @@
       <family val="2"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="7">
     <fill>
@@ -540,7 +639,7 @@
     <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -562,12 +661,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="168" fontId="13" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="2" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="left"/>
       <protection locked="0"/>
@@ -627,6 +720,31 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="168" fontId="13" fillId="2" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyProtection="1">
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1" applyProtection="1">
+      <alignment vertical="center"/>
+      <protection locked="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Hiperlink" xfId="3" builtinId="8"/>
@@ -637,42 +755,6 @@
     <cellStyle name="Vírgula" xfId="4" builtinId="3"/>
   </cellStyles>
   <dxfs count="5">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color theme="1"/>
-        <name val="Aptos Narrow"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <protection locked="0" hidden="0"/>
-    </dxf>
     <dxf>
       <font>
         <strike val="0"/>
@@ -731,13 +813,49 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <protection locked="0" hidden="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color theme="1"/>
+        <name val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <protection locked="0" hidden="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <mruColors>
+      <color rgb="FF0B2D4F"/>
       <color rgb="FFC5D9EA"/>
       <color rgb="FFA9C6E0"/>
-      <color rgb="FF0B2D4F"/>
       <color rgb="FFEAF2F8"/>
       <color rgb="FF0878D1"/>
       <color rgb="FF0E1317"/>
@@ -757,6 +875,75 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>7764780</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>9928860</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>7620</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="Retângulo: Cantos Arredondados 1">
+          <a:hlinkClick xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C943D6B7-0F8A-20E0-08FE-DC8C34BA50A6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7764780" y="1943100"/>
+          <a:ext cx="2164080" cy="449580"/>
+        </a:xfrm>
+        <a:prstGeom prst="roundRect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="pt-BR" sz="1100"/>
+            <a:t>Próximo -&gt; </a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
@@ -1502,7 +1689,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
@@ -2264,7 +2451,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="absolute">
     <xdr:from>
@@ -2963,12 +3150,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16880DCC-BA55-41DD-A6AF-647739D83E49}" name="Tabela1" displayName="Tabela1" ref="C7:E38" totalsRowShown="0" headerRowDxfId="1" dataDxfId="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{16880DCC-BA55-41DD-A6AF-647739D83E49}" name="Tabela1" displayName="Tabela1" ref="C7:E38" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
   <autoFilter ref="C7:E38" xr:uid="{16880DCC-BA55-41DD-A6AF-647739D83E49}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{821F1CB5-5CB2-4C3B-B308-17EC46259109}" name="DATA" dataDxfId="4"/>
-    <tableColumn id="2" xr3:uid="{06693726-1C41-49BB-9967-B8A9B13B3417}" name="CATEGORIA" dataDxfId="3"/>
-    <tableColumn id="3" xr3:uid="{5B9A27AA-3C01-441B-8D9F-663E3F02CD68}" name="VALOR" dataDxfId="2"/>
+    <tableColumn id="1" xr3:uid="{821F1CB5-5CB2-4C3B-B308-17EC46259109}" name="DATA" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{06693726-1C41-49BB-9967-B8A9B13B3417}" name="CATEGORIA" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{5B9A27AA-3C01-441B-8D9F-663E3F02CD68}" name="VALOR" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3290,6 +3477,200 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F0401C6-7197-468F-8E17-33A35D2A6F56}">
+  <sheetPr>
+    <tabColor rgb="FF0B2D4F"/>
+  </sheetPr>
+  <dimension ref="A1:A44"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="149.33203125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" ht="31.2" x14ac:dyDescent="0.3">
+      <c r="A1" s="34" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="27"/>
+    </row>
+    <row r="3" spans="1:1" ht="23.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="30" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="27"/>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="27" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="27"/>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="27" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="27"/>
+    </row>
+    <row r="9" spans="1:1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A9" s="31" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="27"/>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="32" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="27" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="27"/>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="32" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="27" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="27"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="32" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="27" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="27"/>
+    </row>
+    <row r="20" spans="1:1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A20" s="31" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="33"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="33" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="33"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="33" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="33"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="33" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="33"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="33" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="33"/>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="33" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="27"/>
+    </row>
+    <row r="32" spans="1:1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A32" s="31" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="27"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="27" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="27"/>
+    </row>
+    <row r="36" spans="1:1" ht="18" x14ac:dyDescent="0.3">
+      <c r="A36" s="31" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="27"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="27" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="27"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="32" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" s="27"/>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" s="27"/>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" s="27"/>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" s="27"/>
+    </row>
+  </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1" selectUnlockedCells="1"/>
+  <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E633144-20C6-4E9A-ABCC-A9F7DDEF1EB3}">
   <sheetPr codeName="Planilha1"/>
   <dimension ref="A2:E18"/>
@@ -3318,7 +3699,7 @@
       <c r="C5" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="13" t="s">
         <v>16</v>
       </c>
     </row>
@@ -3327,7 +3708,7 @@
       <c r="C6" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="14">
         <v>43536053397</v>
       </c>
     </row>
@@ -3336,7 +3717,7 @@
       <c r="C7" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="D7" s="17">
+      <c r="D7" s="15">
         <v>34600</v>
       </c>
     </row>
@@ -3345,7 +3726,7 @@
       <c r="C8" s="4" t="s">
         <v>3</v>
       </c>
-      <c r="D8" s="15">
+      <c r="D8" s="13">
         <v>31713388</v>
       </c>
     </row>
@@ -3354,7 +3735,7 @@
       <c r="C9" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="D9" s="15" t="s">
+      <c r="D9" s="13" t="s">
         <v>19</v>
       </c>
     </row>
@@ -3363,7 +3744,7 @@
       <c r="C10" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="D10" s="15" t="s">
+      <c r="D10" s="13" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3372,7 +3753,7 @@
       <c r="C11" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="D11" s="15" t="s">
+      <c r="D11" s="13" t="s">
         <v>18</v>
       </c>
     </row>
@@ -3381,7 +3762,7 @@
       <c r="C12" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="D12" s="18">
+      <c r="D12" s="16">
         <v>13154603</v>
       </c>
     </row>
@@ -3389,7 +3770,7 @@
       <c r="C13" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="19">
+      <c r="D13" s="17">
         <v>1131713388</v>
       </c>
     </row>
@@ -3397,7 +3778,7 @@
       <c r="C14" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="18">
         <v>17992713388</v>
       </c>
     </row>
@@ -3405,7 +3786,7 @@
       <c r="C15" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="19" t="s">
         <v>17</v>
       </c>
     </row>
@@ -3413,7 +3794,7 @@
       <c r="C16" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D16" s="13" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3421,7 +3802,7 @@
       <c r="C17" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="15" t="s">
+      <c r="D17" s="13" t="s">
         <v>15</v>
       </c>
     </row>
@@ -3429,13 +3810,13 @@
       <c r="C18" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="15" t="s">
+      <c r="D18" s="13" t="s">
         <v>15</v>
       </c>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
-  <dataValidations disablePrompts="1" count="1">
+  <dataValidations count="1">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D16:D18" xr:uid="{D1F93EA8-29AA-4E0A-84A7-9CC34430080F}">
       <formula1>"SIM,NÃO"</formula1>
     </dataValidation>
@@ -3449,7 +3830,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{603D2FB7-B533-4A68-9EFD-CF9A7C57689B}">
   <sheetPr codeName="Planilha2"/>
   <dimension ref="A2:E26"/>
@@ -3481,11 +3862,11 @@
     </row>
     <row r="6" spans="2:5" ht="19.8" x14ac:dyDescent="0.4">
       <c r="B6" s="2"/>
-      <c r="C6" s="13">
+      <c r="C6" s="28">
         <f>SUM(D10,D15,D20)</f>
         <v>115000</v>
       </c>
-      <c r="D6" s="13"/>
+      <c r="D6" s="28"/>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B7" s="2"/>
@@ -3501,7 +3882,7 @@
       <c r="C9" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="20" t="s">
         <v>45</v>
       </c>
     </row>
@@ -3510,7 +3891,7 @@
       <c r="C10" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="21">
         <v>50000</v>
       </c>
     </row>
@@ -3519,7 +3900,7 @@
       <c r="C11" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D11" s="22" t="s">
+      <c r="D11" s="20" t="s">
         <v>25</v>
       </c>
     </row>
@@ -3537,7 +3918,7 @@
       <c r="C14" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D14" s="22" t="s">
+      <c r="D14" s="20" t="s">
         <v>46</v>
       </c>
     </row>
@@ -3545,7 +3926,7 @@
       <c r="C15" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="21">
         <v>60000</v>
       </c>
     </row>
@@ -3553,7 +3934,7 @@
       <c r="C16" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D16" s="22" t="s">
+      <c r="D16" s="20" t="s">
         <v>25</v>
       </c>
     </row>
@@ -3566,7 +3947,7 @@
       <c r="C19" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="D19" s="20" t="s">
         <v>41</v>
       </c>
     </row>
@@ -3574,7 +3955,7 @@
       <c r="C20" s="11" t="s">
         <v>23</v>
       </c>
-      <c r="D20" s="23">
+      <c r="D20" s="21">
         <v>5000</v>
       </c>
     </row>
@@ -3582,7 +3963,7 @@
       <c r="C21" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="20" t="s">
         <v>25</v>
       </c>
     </row>
@@ -3620,7 +4001,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9ACD4BAE-56EC-4991-AA3F-0B4D9AA8EA87}">
   <sheetPr codeName="Planilha3"/>
   <dimension ref="A2:E116"/>
@@ -3648,597 +4029,597 @@
     </row>
     <row r="6" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6" s="2"/>
-      <c r="C6" s="14" t="s">
+      <c r="C6" s="29" t="s">
         <v>87</v>
       </c>
-      <c r="D6" s="14"/>
-      <c r="E6" s="14"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
     </row>
     <row r="7" spans="2:5" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B7" s="2"/>
-      <c r="C7" s="28" t="s">
+      <c r="C7" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="D7" s="28" t="s">
+      <c r="D7" s="26" t="s">
         <v>85</v>
       </c>
-      <c r="E7" s="28" t="s">
+      <c r="E7" s="26" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="8" spans="2:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B8" s="2"/>
-      <c r="C8" s="24">
+      <c r="C8" s="22">
         <v>46235</v>
       </c>
-      <c r="D8" s="25" t="s">
+      <c r="D8" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="E8" s="26">
+      <c r="E8" s="24">
         <v>5000</v>
       </c>
     </row>
     <row r="9" spans="2:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B9" s="2"/>
-      <c r="C9" s="24">
+      <c r="C9" s="22">
         <v>46280</v>
       </c>
-      <c r="D9" s="25" t="s">
+      <c r="D9" s="23" t="s">
         <v>89</v>
       </c>
-      <c r="E9" s="26">
+      <c r="E9" s="24">
         <v>10000</v>
       </c>
     </row>
     <row r="10" spans="2:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B10" s="2"/>
-      <c r="C10" s="24">
+      <c r="C10" s="22">
         <v>46285</v>
       </c>
-      <c r="D10" s="25" t="s">
+      <c r="D10" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="E10" s="26">
+      <c r="E10" s="24">
         <v>5000</v>
       </c>
     </row>
     <row r="11" spans="2:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B11" s="2"/>
-      <c r="C11" s="24">
+      <c r="C11" s="22">
         <v>46315</v>
       </c>
-      <c r="D11" s="25" t="s">
+      <c r="D11" s="23" t="s">
         <v>88</v>
       </c>
-      <c r="E11" s="26">
+      <c r="E11" s="24">
         <v>5000</v>
       </c>
     </row>
     <row r="12" spans="2:5" ht="16.8" x14ac:dyDescent="0.3">
       <c r="B12" s="2"/>
-      <c r="C12" s="24"/>
-      <c r="D12" s="25"/>
-      <c r="E12" s="26"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="23"/>
+      <c r="E12" s="24"/>
     </row>
     <row r="13" spans="2:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C13" s="24"/>
-      <c r="D13" s="25"/>
-      <c r="E13" s="26"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="24"/>
     </row>
     <row r="14" spans="2:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C14" s="24"/>
-      <c r="D14" s="25"/>
-      <c r="E14" s="26"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="23"/>
+      <c r="E14" s="24"/>
     </row>
     <row r="15" spans="2:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C15" s="24"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="26"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="23"/>
+      <c r="E15" s="24"/>
     </row>
     <row r="16" spans="2:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C16" s="24"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="26"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="23"/>
+      <c r="E16" s="24"/>
     </row>
     <row r="17" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C17" s="24"/>
-      <c r="D17" s="25"/>
-      <c r="E17" s="26"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="23"/>
+      <c r="E17" s="24"/>
     </row>
     <row r="18" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C18" s="24"/>
-      <c r="D18" s="25"/>
-      <c r="E18" s="26"/>
+      <c r="C18" s="22"/>
+      <c r="D18" s="23"/>
+      <c r="E18" s="24"/>
     </row>
     <row r="19" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C19" s="24"/>
-      <c r="D19" s="25"/>
-      <c r="E19" s="26"/>
+      <c r="C19" s="22"/>
+      <c r="D19" s="23"/>
+      <c r="E19" s="24"/>
     </row>
     <row r="20" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C20" s="24"/>
-      <c r="D20" s="25"/>
-      <c r="E20" s="26"/>
+      <c r="C20" s="22"/>
+      <c r="D20" s="23"/>
+      <c r="E20" s="24"/>
     </row>
     <row r="21" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C21" s="24"/>
-      <c r="D21" s="25"/>
-      <c r="E21" s="26"/>
+      <c r="C21" s="22"/>
+      <c r="D21" s="23"/>
+      <c r="E21" s="24"/>
     </row>
     <row r="22" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C22" s="24"/>
-      <c r="D22" s="25"/>
-      <c r="E22" s="26"/>
+      <c r="C22" s="22"/>
+      <c r="D22" s="23"/>
+      <c r="E22" s="24"/>
     </row>
     <row r="23" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C23" s="24"/>
-      <c r="D23" s="25"/>
-      <c r="E23" s="26"/>
+      <c r="C23" s="22"/>
+      <c r="D23" s="23"/>
+      <c r="E23" s="24"/>
     </row>
     <row r="24" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C24" s="24"/>
-      <c r="D24" s="25"/>
-      <c r="E24" s="26"/>
+      <c r="C24" s="22"/>
+      <c r="D24" s="23"/>
+      <c r="E24" s="24"/>
     </row>
     <row r="25" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C25" s="24"/>
-      <c r="D25" s="25"/>
-      <c r="E25" s="26"/>
+      <c r="C25" s="22"/>
+      <c r="D25" s="23"/>
+      <c r="E25" s="24"/>
     </row>
     <row r="26" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C26" s="24"/>
-      <c r="D26" s="25"/>
-      <c r="E26" s="26"/>
+      <c r="C26" s="22"/>
+      <c r="D26" s="23"/>
+      <c r="E26" s="24"/>
     </row>
     <row r="27" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C27" s="24"/>
-      <c r="D27" s="25"/>
-      <c r="E27" s="26"/>
+      <c r="C27" s="22"/>
+      <c r="D27" s="23"/>
+      <c r="E27" s="24"/>
     </row>
     <row r="28" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C28" s="24"/>
-      <c r="D28" s="25"/>
-      <c r="E28" s="26"/>
+      <c r="C28" s="22"/>
+      <c r="D28" s="23"/>
+      <c r="E28" s="24"/>
     </row>
     <row r="29" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C29" s="24"/>
-      <c r="D29" s="25"/>
-      <c r="E29" s="26"/>
+      <c r="C29" s="22"/>
+      <c r="D29" s="23"/>
+      <c r="E29" s="24"/>
     </row>
     <row r="30" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C30" s="24"/>
-      <c r="D30" s="25"/>
-      <c r="E30" s="26"/>
+      <c r="C30" s="22"/>
+      <c r="D30" s="23"/>
+      <c r="E30" s="24"/>
     </row>
     <row r="31" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C31" s="24"/>
-      <c r="D31" s="25"/>
-      <c r="E31" s="27"/>
+      <c r="C31" s="22"/>
+      <c r="D31" s="23"/>
+      <c r="E31" s="25"/>
     </row>
     <row r="32" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C32" s="24"/>
-      <c r="D32" s="25"/>
-      <c r="E32" s="27"/>
+      <c r="C32" s="22"/>
+      <c r="D32" s="23"/>
+      <c r="E32" s="25"/>
     </row>
     <row r="33" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C33" s="24"/>
-      <c r="D33" s="25"/>
-      <c r="E33" s="27"/>
+      <c r="C33" s="22"/>
+      <c r="D33" s="23"/>
+      <c r="E33" s="25"/>
     </row>
     <row r="34" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C34" s="24"/>
-      <c r="D34" s="25"/>
-      <c r="E34" s="27"/>
+      <c r="C34" s="22"/>
+      <c r="D34" s="23"/>
+      <c r="E34" s="25"/>
     </row>
     <row r="35" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C35" s="24"/>
-      <c r="D35" s="25"/>
-      <c r="E35" s="27"/>
+      <c r="C35" s="22"/>
+      <c r="D35" s="23"/>
+      <c r="E35" s="25"/>
     </row>
     <row r="36" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C36" s="24"/>
-      <c r="D36" s="25"/>
-      <c r="E36" s="27"/>
+      <c r="C36" s="22"/>
+      <c r="D36" s="23"/>
+      <c r="E36" s="25"/>
     </row>
     <row r="37" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C37" s="24"/>
-      <c r="D37" s="25"/>
-      <c r="E37" s="27"/>
+      <c r="C37" s="22"/>
+      <c r="D37" s="23"/>
+      <c r="E37" s="25"/>
     </row>
     <row r="38" spans="3:5" ht="16.8" x14ac:dyDescent="0.3">
-      <c r="C38" s="24"/>
-      <c r="D38" s="25"/>
-      <c r="E38" s="27"/>
+      <c r="C38" s="22"/>
+      <c r="D38" s="23"/>
+      <c r="E38" s="25"/>
     </row>
     <row r="39" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C39" s="29"/>
-      <c r="D39" s="29"/>
-      <c r="E39" s="29"/>
+      <c r="C39" s="27"/>
+      <c r="D39" s="27"/>
+      <c r="E39" s="27"/>
     </row>
     <row r="40" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C40" s="29"/>
-      <c r="D40" s="29"/>
-      <c r="E40" s="29"/>
+      <c r="C40" s="27"/>
+      <c r="D40" s="27"/>
+      <c r="E40" s="27"/>
     </row>
     <row r="41" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C41" s="29"/>
-      <c r="D41" s="29"/>
-      <c r="E41" s="29"/>
+      <c r="C41" s="27"/>
+      <c r="D41" s="27"/>
+      <c r="E41" s="27"/>
     </row>
     <row r="42" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C42" s="29"/>
-      <c r="D42" s="29"/>
-      <c r="E42" s="29"/>
+      <c r="C42" s="27"/>
+      <c r="D42" s="27"/>
+      <c r="E42" s="27"/>
     </row>
     <row r="43" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C43" s="29"/>
-      <c r="D43" s="29"/>
-      <c r="E43" s="29"/>
+      <c r="C43" s="27"/>
+      <c r="D43" s="27"/>
+      <c r="E43" s="27"/>
     </row>
     <row r="44" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C44" s="29"/>
-      <c r="D44" s="29"/>
-      <c r="E44" s="29"/>
+      <c r="C44" s="27"/>
+      <c r="D44" s="27"/>
+      <c r="E44" s="27"/>
     </row>
     <row r="45" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C45" s="29"/>
-      <c r="D45" s="29"/>
-      <c r="E45" s="29"/>
+      <c r="C45" s="27"/>
+      <c r="D45" s="27"/>
+      <c r="E45" s="27"/>
     </row>
     <row r="46" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C46" s="29"/>
-      <c r="D46" s="29"/>
-      <c r="E46" s="29"/>
+      <c r="C46" s="27"/>
+      <c r="D46" s="27"/>
+      <c r="E46" s="27"/>
     </row>
     <row r="47" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C47" s="29"/>
-      <c r="D47" s="29"/>
-      <c r="E47" s="29"/>
+      <c r="C47" s="27"/>
+      <c r="D47" s="27"/>
+      <c r="E47" s="27"/>
     </row>
     <row r="48" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C48" s="29"/>
-      <c r="D48" s="29"/>
-      <c r="E48" s="29"/>
+      <c r="C48" s="27"/>
+      <c r="D48" s="27"/>
+      <c r="E48" s="27"/>
     </row>
     <row r="49" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C49" s="29"/>
-      <c r="D49" s="29"/>
-      <c r="E49" s="29"/>
+      <c r="C49" s="27"/>
+      <c r="D49" s="27"/>
+      <c r="E49" s="27"/>
     </row>
     <row r="50" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C50" s="29"/>
-      <c r="D50" s="29"/>
-      <c r="E50" s="29"/>
+      <c r="C50" s="27"/>
+      <c r="D50" s="27"/>
+      <c r="E50" s="27"/>
     </row>
     <row r="51" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C51" s="29"/>
-      <c r="D51" s="29"/>
-      <c r="E51" s="29"/>
+      <c r="C51" s="27"/>
+      <c r="D51" s="27"/>
+      <c r="E51" s="27"/>
     </row>
     <row r="52" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C52" s="29"/>
-      <c r="D52" s="29"/>
-      <c r="E52" s="29"/>
+      <c r="C52" s="27"/>
+      <c r="D52" s="27"/>
+      <c r="E52" s="27"/>
     </row>
     <row r="53" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C53" s="29"/>
-      <c r="D53" s="29"/>
-      <c r="E53" s="29"/>
+      <c r="C53" s="27"/>
+      <c r="D53" s="27"/>
+      <c r="E53" s="27"/>
     </row>
     <row r="54" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C54" s="29"/>
-      <c r="D54" s="29"/>
-      <c r="E54" s="29"/>
+      <c r="C54" s="27"/>
+      <c r="D54" s="27"/>
+      <c r="E54" s="27"/>
     </row>
     <row r="55" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C55" s="29"/>
-      <c r="D55" s="29"/>
-      <c r="E55" s="29"/>
+      <c r="C55" s="27"/>
+      <c r="D55" s="27"/>
+      <c r="E55" s="27"/>
     </row>
     <row r="56" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C56" s="29"/>
-      <c r="D56" s="29"/>
-      <c r="E56" s="29"/>
+      <c r="C56" s="27"/>
+      <c r="D56" s="27"/>
+      <c r="E56" s="27"/>
     </row>
     <row r="57" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C57" s="29"/>
-      <c r="D57" s="29"/>
-      <c r="E57" s="29"/>
+      <c r="C57" s="27"/>
+      <c r="D57" s="27"/>
+      <c r="E57" s="27"/>
     </row>
     <row r="58" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C58" s="29"/>
-      <c r="D58" s="29"/>
-      <c r="E58" s="29"/>
+      <c r="C58" s="27"/>
+      <c r="D58" s="27"/>
+      <c r="E58" s="27"/>
     </row>
     <row r="59" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C59" s="29"/>
-      <c r="D59" s="29"/>
-      <c r="E59" s="29"/>
+      <c r="C59" s="27"/>
+      <c r="D59" s="27"/>
+      <c r="E59" s="27"/>
     </row>
     <row r="60" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C60" s="29"/>
-      <c r="D60" s="29"/>
-      <c r="E60" s="29"/>
+      <c r="C60" s="27"/>
+      <c r="D60" s="27"/>
+      <c r="E60" s="27"/>
     </row>
     <row r="61" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C61" s="29"/>
-      <c r="D61" s="29"/>
-      <c r="E61" s="29"/>
+      <c r="C61" s="27"/>
+      <c r="D61" s="27"/>
+      <c r="E61" s="27"/>
     </row>
     <row r="62" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C62" s="29"/>
-      <c r="D62" s="29"/>
-      <c r="E62" s="29"/>
+      <c r="C62" s="27"/>
+      <c r="D62" s="27"/>
+      <c r="E62" s="27"/>
     </row>
     <row r="63" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C63" s="29"/>
-      <c r="D63" s="29"/>
-      <c r="E63" s="29"/>
+      <c r="C63" s="27"/>
+      <c r="D63" s="27"/>
+      <c r="E63" s="27"/>
     </row>
     <row r="64" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C64" s="29"/>
-      <c r="D64" s="29"/>
-      <c r="E64" s="29"/>
+      <c r="C64" s="27"/>
+      <c r="D64" s="27"/>
+      <c r="E64" s="27"/>
     </row>
     <row r="65" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C65" s="29"/>
-      <c r="D65" s="29"/>
-      <c r="E65" s="29"/>
+      <c r="C65" s="27"/>
+      <c r="D65" s="27"/>
+      <c r="E65" s="27"/>
     </row>
     <row r="66" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C66" s="29"/>
-      <c r="D66" s="29"/>
-      <c r="E66" s="29"/>
+      <c r="C66" s="27"/>
+      <c r="D66" s="27"/>
+      <c r="E66" s="27"/>
     </row>
     <row r="67" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C67" s="29"/>
-      <c r="D67" s="29"/>
-      <c r="E67" s="29"/>
+      <c r="C67" s="27"/>
+      <c r="D67" s="27"/>
+      <c r="E67" s="27"/>
     </row>
     <row r="68" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C68" s="29"/>
-      <c r="D68" s="29"/>
-      <c r="E68" s="29"/>
+      <c r="C68" s="27"/>
+      <c r="D68" s="27"/>
+      <c r="E68" s="27"/>
     </row>
     <row r="69" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C69" s="29"/>
-      <c r="D69" s="29"/>
-      <c r="E69" s="29"/>
+      <c r="C69" s="27"/>
+      <c r="D69" s="27"/>
+      <c r="E69" s="27"/>
     </row>
     <row r="70" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C70" s="29"/>
-      <c r="D70" s="29"/>
-      <c r="E70" s="29"/>
+      <c r="C70" s="27"/>
+      <c r="D70" s="27"/>
+      <c r="E70" s="27"/>
     </row>
     <row r="71" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C71" s="29"/>
-      <c r="D71" s="29"/>
-      <c r="E71" s="29"/>
+      <c r="C71" s="27"/>
+      <c r="D71" s="27"/>
+      <c r="E71" s="27"/>
     </row>
     <row r="72" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C72" s="29"/>
-      <c r="D72" s="29"/>
-      <c r="E72" s="29"/>
+      <c r="C72" s="27"/>
+      <c r="D72" s="27"/>
+      <c r="E72" s="27"/>
     </row>
     <row r="73" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C73" s="29"/>
-      <c r="D73" s="29"/>
-      <c r="E73" s="29"/>
+      <c r="C73" s="27"/>
+      <c r="D73" s="27"/>
+      <c r="E73" s="27"/>
     </row>
     <row r="74" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C74" s="29"/>
-      <c r="D74" s="29"/>
-      <c r="E74" s="29"/>
+      <c r="C74" s="27"/>
+      <c r="D74" s="27"/>
+      <c r="E74" s="27"/>
     </row>
     <row r="75" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C75" s="29"/>
-      <c r="D75" s="29"/>
-      <c r="E75" s="29"/>
+      <c r="C75" s="27"/>
+      <c r="D75" s="27"/>
+      <c r="E75" s="27"/>
     </row>
     <row r="76" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C76" s="29"/>
-      <c r="D76" s="29"/>
-      <c r="E76" s="29"/>
+      <c r="C76" s="27"/>
+      <c r="D76" s="27"/>
+      <c r="E76" s="27"/>
     </row>
     <row r="77" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C77" s="29"/>
-      <c r="D77" s="29"/>
-      <c r="E77" s="29"/>
+      <c r="C77" s="27"/>
+      <c r="D77" s="27"/>
+      <c r="E77" s="27"/>
     </row>
     <row r="78" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C78" s="29"/>
-      <c r="D78" s="29"/>
-      <c r="E78" s="29"/>
+      <c r="C78" s="27"/>
+      <c r="D78" s="27"/>
+      <c r="E78" s="27"/>
     </row>
     <row r="79" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C79" s="29"/>
-      <c r="D79" s="29"/>
-      <c r="E79" s="29"/>
+      <c r="C79" s="27"/>
+      <c r="D79" s="27"/>
+      <c r="E79" s="27"/>
     </row>
     <row r="80" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C80" s="29"/>
-      <c r="D80" s="29"/>
-      <c r="E80" s="29"/>
+      <c r="C80" s="27"/>
+      <c r="D80" s="27"/>
+      <c r="E80" s="27"/>
     </row>
     <row r="81" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C81" s="29"/>
-      <c r="D81" s="29"/>
-      <c r="E81" s="29"/>
+      <c r="C81" s="27"/>
+      <c r="D81" s="27"/>
+      <c r="E81" s="27"/>
     </row>
     <row r="82" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C82" s="29"/>
-      <c r="D82" s="29"/>
-      <c r="E82" s="29"/>
+      <c r="C82" s="27"/>
+      <c r="D82" s="27"/>
+      <c r="E82" s="27"/>
     </row>
     <row r="83" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C83" s="29"/>
-      <c r="D83" s="29"/>
-      <c r="E83" s="29"/>
+      <c r="C83" s="27"/>
+      <c r="D83" s="27"/>
+      <c r="E83" s="27"/>
     </row>
     <row r="84" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C84" s="29"/>
-      <c r="D84" s="29"/>
-      <c r="E84" s="29"/>
+      <c r="C84" s="27"/>
+      <c r="D84" s="27"/>
+      <c r="E84" s="27"/>
     </row>
     <row r="85" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C85" s="29"/>
-      <c r="D85" s="29"/>
-      <c r="E85" s="29"/>
+      <c r="C85" s="27"/>
+      <c r="D85" s="27"/>
+      <c r="E85" s="27"/>
     </row>
     <row r="86" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C86" s="29"/>
-      <c r="D86" s="29"/>
-      <c r="E86" s="29"/>
+      <c r="C86" s="27"/>
+      <c r="D86" s="27"/>
+      <c r="E86" s="27"/>
     </row>
     <row r="87" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C87" s="29"/>
-      <c r="D87" s="29"/>
-      <c r="E87" s="29"/>
+      <c r="C87" s="27"/>
+      <c r="D87" s="27"/>
+      <c r="E87" s="27"/>
     </row>
     <row r="88" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C88" s="29"/>
-      <c r="D88" s="29"/>
-      <c r="E88" s="29"/>
+      <c r="C88" s="27"/>
+      <c r="D88" s="27"/>
+      <c r="E88" s="27"/>
     </row>
     <row r="89" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C89" s="29"/>
-      <c r="D89" s="29"/>
-      <c r="E89" s="29"/>
+      <c r="C89" s="27"/>
+      <c r="D89" s="27"/>
+      <c r="E89" s="27"/>
     </row>
     <row r="90" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C90" s="29"/>
-      <c r="D90" s="29"/>
-      <c r="E90" s="29"/>
+      <c r="C90" s="27"/>
+      <c r="D90" s="27"/>
+      <c r="E90" s="27"/>
     </row>
     <row r="91" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C91" s="29"/>
-      <c r="D91" s="29"/>
-      <c r="E91" s="29"/>
+      <c r="C91" s="27"/>
+      <c r="D91" s="27"/>
+      <c r="E91" s="27"/>
     </row>
     <row r="92" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C92" s="29"/>
-      <c r="D92" s="29"/>
-      <c r="E92" s="29"/>
+      <c r="C92" s="27"/>
+      <c r="D92" s="27"/>
+      <c r="E92" s="27"/>
     </row>
     <row r="93" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C93" s="29"/>
-      <c r="D93" s="29"/>
-      <c r="E93" s="29"/>
+      <c r="C93" s="27"/>
+      <c r="D93" s="27"/>
+      <c r="E93" s="27"/>
     </row>
     <row r="94" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C94" s="29"/>
-      <c r="D94" s="29"/>
-      <c r="E94" s="29"/>
+      <c r="C94" s="27"/>
+      <c r="D94" s="27"/>
+      <c r="E94" s="27"/>
     </row>
     <row r="95" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C95" s="29"/>
-      <c r="D95" s="29"/>
-      <c r="E95" s="29"/>
+      <c r="C95" s="27"/>
+      <c r="D95" s="27"/>
+      <c r="E95" s="27"/>
     </row>
     <row r="96" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C96" s="29"/>
-      <c r="D96" s="29"/>
-      <c r="E96" s="29"/>
+      <c r="C96" s="27"/>
+      <c r="D96" s="27"/>
+      <c r="E96" s="27"/>
     </row>
     <row r="97" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C97" s="29"/>
-      <c r="D97" s="29"/>
-      <c r="E97" s="29"/>
+      <c r="C97" s="27"/>
+      <c r="D97" s="27"/>
+      <c r="E97" s="27"/>
     </row>
     <row r="98" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C98" s="29"/>
-      <c r="D98" s="29"/>
-      <c r="E98" s="29"/>
+      <c r="C98" s="27"/>
+      <c r="D98" s="27"/>
+      <c r="E98" s="27"/>
     </row>
     <row r="99" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C99" s="29"/>
-      <c r="D99" s="29"/>
-      <c r="E99" s="29"/>
+      <c r="C99" s="27"/>
+      <c r="D99" s="27"/>
+      <c r="E99" s="27"/>
     </row>
     <row r="100" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C100" s="29"/>
-      <c r="D100" s="29"/>
-      <c r="E100" s="29"/>
+      <c r="C100" s="27"/>
+      <c r="D100" s="27"/>
+      <c r="E100" s="27"/>
     </row>
     <row r="101" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C101" s="29"/>
-      <c r="D101" s="29"/>
-      <c r="E101" s="29"/>
+      <c r="C101" s="27"/>
+      <c r="D101" s="27"/>
+      <c r="E101" s="27"/>
     </row>
     <row r="102" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C102" s="29"/>
-      <c r="D102" s="29"/>
-      <c r="E102" s="29"/>
+      <c r="C102" s="27"/>
+      <c r="D102" s="27"/>
+      <c r="E102" s="27"/>
     </row>
     <row r="103" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C103" s="29"/>
-      <c r="D103" s="29"/>
-      <c r="E103" s="29"/>
+      <c r="C103" s="27"/>
+      <c r="D103" s="27"/>
+      <c r="E103" s="27"/>
     </row>
     <row r="104" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C104" s="29"/>
-      <c r="D104" s="29"/>
-      <c r="E104" s="29"/>
+      <c r="C104" s="27"/>
+      <c r="D104" s="27"/>
+      <c r="E104" s="27"/>
     </row>
     <row r="105" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C105" s="29"/>
-      <c r="D105" s="29"/>
-      <c r="E105" s="29"/>
+      <c r="C105" s="27"/>
+      <c r="D105" s="27"/>
+      <c r="E105" s="27"/>
     </row>
     <row r="106" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C106" s="29"/>
-      <c r="D106" s="29"/>
-      <c r="E106" s="29"/>
+      <c r="C106" s="27"/>
+      <c r="D106" s="27"/>
+      <c r="E106" s="27"/>
     </row>
     <row r="107" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C107" s="29"/>
-      <c r="D107" s="29"/>
-      <c r="E107" s="29"/>
+      <c r="C107" s="27"/>
+      <c r="D107" s="27"/>
+      <c r="E107" s="27"/>
     </row>
     <row r="108" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C108" s="29"/>
-      <c r="D108" s="29"/>
-      <c r="E108" s="29"/>
+      <c r="C108" s="27"/>
+      <c r="D108" s="27"/>
+      <c r="E108" s="27"/>
     </row>
     <row r="109" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C109" s="29"/>
-      <c r="D109" s="29"/>
-      <c r="E109" s="29"/>
+      <c r="C109" s="27"/>
+      <c r="D109" s="27"/>
+      <c r="E109" s="27"/>
     </row>
     <row r="110" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C110" s="29"/>
-      <c r="D110" s="29"/>
-      <c r="E110" s="29"/>
+      <c r="C110" s="27"/>
+      <c r="D110" s="27"/>
+      <c r="E110" s="27"/>
     </row>
     <row r="111" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C111" s="29"/>
-      <c r="D111" s="29"/>
-      <c r="E111" s="29"/>
+      <c r="C111" s="27"/>
+      <c r="D111" s="27"/>
+      <c r="E111" s="27"/>
     </row>
     <row r="112" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C112" s="29"/>
-      <c r="D112" s="29"/>
-      <c r="E112" s="29"/>
+      <c r="C112" s="27"/>
+      <c r="D112" s="27"/>
+      <c r="E112" s="27"/>
     </row>
     <row r="113" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C113" s="29"/>
-      <c r="D113" s="29"/>
-      <c r="E113" s="29"/>
+      <c r="C113" s="27"/>
+      <c r="D113" s="27"/>
+      <c r="E113" s="27"/>
     </row>
     <row r="114" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C114" s="29"/>
-      <c r="D114" s="29"/>
-      <c r="E114" s="29"/>
+      <c r="C114" s="27"/>
+      <c r="D114" s="27"/>
+      <c r="E114" s="27"/>
     </row>
     <row r="115" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C115" s="29"/>
-      <c r="D115" s="29"/>
-      <c r="E115" s="29"/>
+      <c r="C115" s="27"/>
+      <c r="D115" s="27"/>
+      <c r="E115" s="27"/>
     </row>
     <row r="116" spans="3:5" x14ac:dyDescent="0.3">
-      <c r="C116" s="29"/>
-      <c r="D116" s="29"/>
-      <c r="E116" s="29"/>
+      <c r="C116" s="27"/>
+      <c r="D116" s="27"/>
+      <c r="E116" s="27"/>
     </row>
   </sheetData>
   <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="1"/>
@@ -4258,7 +4639,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F78ED27-9201-4528-94F9-E867CE99B571}">
   <dimension ref="A1:A51"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
